--- a/assets/class4/ecommerce.xlsx
+++ b/assets/class4/ecommerce.xlsx
@@ -370,7 +370,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1609fdd7-29c6-4678-84af-30684d709f0b</t>
+          <t>d69b50f2-d432-4e62-8eb6-544c16ea8f91</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -382,7 +382,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1064a4dc-df76-4aba-8b74-953a4c66fa16</t>
+          <t>29d3e3d9-da12-4f22-83f3-9671acea6310</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -394,7 +394,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>155e9331-3434-415f-9d66-67736534d80b</t>
+          <t>c79ca409-badc-4ec1-988b-e315cf9674cd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -406,7 +406,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>105696b8-7c38-4fe5-92f5-3c6fb1268f48</t>
+          <t>e7867498-1e26-4f63-8ead-766e787f4bc7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12175814-556e-4e1a-af05-0c38c13e98a0</t>
+          <t>aacac9c8-54cd-4409-bdfe-f60c5e965799</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>80fb4c6d-d5f8-42ed-b3c7-8a10596dd382</t>
+          <t>31fae897-0630-4862-aabf-e709ff39752b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -442,7 +442,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -454,7 +454,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cea15e94-869f-417a-9ad4-a70aefc74f34</t>
+          <t>68ac6965-f822-4e2a-8394-c81b5bce9ac9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -466,7 +466,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8b0a0720-0487-44d2-9aae-32dfec5c4b5c</t>
+          <t>4be511d9-1baa-4ed1-8ce8-db7161fce0fe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -478,7 +478,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>578ffa9d-ec4c-4a54-8a32-6f15ac4deb53</t>
+          <t>533d0a29-8ed3-4625-af16-a0f4f9e0c2f0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -490,7 +490,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>80fb4c6d-d5f8-42ed-b3c7-8a10596dd382</t>
+          <t>31fae897-0630-4862-aabf-e709ff39752b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -502,7 +502,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9721f3a7-07aa-4c78-8332-8d1ebfbf9d3a</t>
+          <t>eb4b3541-a786-4a3f-adf2-8ff4d17d6c27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54fca07c-27a4-4f19-9e12-68cdab4aa082</t>
+          <t>e02d1641-7b75-4057-a560-ee615b79013f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8d95429e-357c-4864-8ab0-6f3936c1a539</t>
+          <t>bfee1f21-d0da-4309-a1d4-59bfadbbf8b2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>035f4bce-3ab1-47b3-bd32-823d20840663</t>
+          <t>966edd62-d24a-482b-b392-7b2fcc95e399</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f326387b-2592-4682-8778-65dde88f3703</t>
+          <t>34dab44f-316b-40bc-acd4-69581e3257f1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5b0e86f3-4bdb-4998-b076-b9294b20086d</t>
+          <t>a68cd6ef-c68a-441e-a830-6b7cab96460a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b6feb9d6-2504-46ca-bd63-cebf56ffa28e</t>
+          <t>01bd484f-97d8-4474-b008-4bb3e9277498</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>485d6fb5-896c-41af-a87c-9efdd3edf92a</t>
+          <t>1e75f7bf-c89f-4366-b367-e68d7b757c47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9aa3b6d8-bb97-45ce-9288-37bbeeb8a16c</t>
+          <t>b6302ed5-3c77-4247-a2b8-6f46e6e831b0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>312876be-484d-47e9-8b5e-4522fad5df43</t>
+          <t>9614b009-6732-4501-bb01-9c3e282d45de</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1609fdd7-29c6-4678-84af-30684d709f0b</t>
+          <t>d69b50f2-d432-4e62-8eb6-544c16ea8f91</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4af34c15-d5c9-462e-85e5-3f15cc0a9d0a</t>
+          <t>37b9167b-d0a7-4565-b505-737fee966821</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>d87ab052-abfa-48dd-84e1-c6a42aaded01</t>
+          <t>93016bc4-790b-4b5f-ac66-176155e6423b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>155e9331-3434-415f-9d66-67736534d80b</t>
+          <t>c79ca409-badc-4ec1-988b-e315cf9674cd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>e5d2b992-4501-42cf-acbb-b6d345e8627a</t>
+          <t>5f7fff9a-1cdf-4a40-86fb-777d241f4777</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a52ab805-8822-4e48-a23a-58eb8d10a72f</t>
+          <t>4c2be30f-a0d3-4071-8d9c-c0c3b2f9a476</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>114e30a1-25ee-419c-814f-5fc37d86252a</t>
+          <t>f626081b-f710-4003-91b0-5471de681880</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0b8609f4-825b-4888-8e37-e56fdfefa560</t>
+          <t>d3fd41d5-7be6-42a4-9e28-e9b2b915dcc6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>75ba12c8-4bcf-46d3-a232-8ceea4f98469</t>
+          <t>24fcc1cf-9d5a-4a7f-9152-10cb2cebe997</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29b4a584-0a8d-496c-8b4c-b71ab5b6926e</t>
+          <t>a24f16c4-5fc6-43d8-b547-688adc5e6e3c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ccb23593-3e4d-4689-aa63-a27741a90d74</t>
+          <t>aa050ea9-0d9e-4a7f-8b39-78ee272ade87</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>b3eb37b0-6525-4ef6-829a-0a98b06cf525</t>
+          <t>d3b64cd8-eea7-4fa6-8765-64a834e023ce</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -862,7 +862,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1e61c945-1942-4e78-b762-12a14b5dd95c</t>
+          <t>ec13fb11-8965-400b-b834-e3cbaa12604a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>008c0375-a8bb-43b1-bc1e-b501f053dd11</t>
+          <t>3a01efce-4062-4761-aca6-cb99a7c5b784</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -886,7 +886,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7978e4db-aa02-481f-a00e-7a31b33a8d57</t>
+          <t>76c21f8c-5942-4431-8178-b97a409b1c39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ccb23593-3e4d-4689-aa63-a27741a90d74</t>
+          <t>aa050ea9-0d9e-4a7f-8b39-78ee272ade87</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>d87ab052-abfa-48dd-84e1-c6a42aaded01</t>
+          <t>93016bc4-790b-4b5f-ac66-176155e6423b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>359a8f68-9347-468a-9e71-2fd7a932482a</t>
+          <t>9278f6ac-147a-4450-ad2f-0662a8bc8f3f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8ebc7d87-92ad-4ead-933b-756e3a609d5a</t>
+          <t>17cd22b6-3a11-4dfd-9395-242ce37db1c2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6d21a58b-bc86-4592-9b5a-bce7e7b9a793</t>
+          <t>711d3c39-6c12-446c-a03d-2afe5918baca</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>eb16c569-d25c-4bc1-bd2d-e124c7fffc31</t>
+          <t>2eaa7d6d-ba2b-47d5-9e17-423646a4fa8a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>035f4bce-3ab1-47b3-bd32-823d20840663</t>
+          <t>966edd62-d24a-482b-b392-7b2fcc95e399</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1042,7 +1042,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9022fcac-7c66-4018-8a63-bed6195c6407</t>
+          <t>db3adcc8-2455-4f90-b655-dc0276edbfbf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5687c94d-9565-4dfb-9767-b96009dcff3b</t>
+          <t>a1579a13-58ec-416d-b32f-e70df61c8c80</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3a7e16bf-a833-42ac-831b-e583c0800e61</t>
+          <t>07bccb94-0c12-4fa0-b866-048a07b43173</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6c5fbef9-45b2-4a20-a301-d1fba1d53fbb</t>
+          <t>839dccbc-54bb-4e7b-80cf-bc6f2d662a11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>d36fc989-0ebe-4ed1-b7ff-3a89ed08191a</t>
+          <t>d5bf0026-742b-4ea1-9fe3-8bdec31b0e45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>d36fc989-0ebe-4ed1-b7ff-3a89ed08191a</t>
+          <t>d5bf0026-742b-4ea1-9fe3-8bdec31b0e45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1e61c945-1942-4e78-b762-12a14b5dd95c</t>
+          <t>ec13fb11-8965-400b-b834-e3cbaa12604a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1e61c945-1942-4e78-b762-12a14b5dd95c</t>
+          <t>ec13fb11-8965-400b-b834-e3cbaa12604a</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a5e2cb8c-f9a7-4e47-afb8-c9e80e7fe925</t>
+          <t>a8930c88-2102-4ee8-897f-060e9f2d09b4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>893445dc-1109-453c-871c-96b9582fb4c3</t>
+          <t>4b376971-d2ea-4cf0-ac14-2883949a2439</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>414becf9-46b2-4d49-975d-ed962aa02e2e</t>
+          <t>9d38d112-d84f-4587-a1eb-5f180ef91214</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6f98d296-c5e7-49d5-b34e-3a3f7c1e112b</t>
+          <t>006e14c2-2615-4cd8-bc46-77c4c58ead5a</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1234,7 +1234,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>933ad94c-2e9f-485c-830a-2ca6c4230d39</t>
+          <t>7ff1ea7e-5828-4e1a-8090-df457f48018f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2b190f8a-b46f-478d-a77d-199659aace3e</t>
+          <t>b940ec08-c742-493a-94e7-7d09ff0f275a</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6d21a58b-bc86-4592-9b5a-bce7e7b9a793</t>
+          <t>711d3c39-6c12-446c-a03d-2afe5918baca</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12175814-556e-4e1a-af05-0c38c13e98a0</t>
+          <t>aacac9c8-54cd-4409-bdfe-f60c5e965799</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9a072dbe-584f-43c4-978b-88dd092f9c90</t>
+          <t>11f2d634-c9ef-4583-ad95-25ca251bd062</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2b190f8a-b46f-478d-a77d-199659aace3e</t>
+          <t>b940ec08-c742-493a-94e7-7d09ff0f275a</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1064a4dc-df76-4aba-8b74-953a4c66fa16</t>
+          <t>29d3e3d9-da12-4f22-83f3-9671acea6310</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6d003f3d-815e-4778-af95-43f0492785e6</t>
+          <t>2476e549-4975-4160-85d8-8def639d3ee8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2f983d15-b4b9-4a43-9ba2-f8d2334b2190</t>
+          <t>1047079d-3655-48f7-a34b-eddb993840fe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>893445dc-1109-453c-871c-96b9582fb4c3</t>
+          <t>4b376971-d2ea-4cf0-ac14-2883949a2439</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6f98d296-c5e7-49d5-b34e-3a3f7c1e112b</t>
+          <t>006e14c2-2615-4cd8-bc46-77c4c58ead5a</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>d27be5c4-3d74-4264-a869-f5ca39930b8d</t>
+          <t>0065711e-d1b5-46aa-b654-f4ae232d118a</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2f983d15-b4b9-4a43-9ba2-f8d2334b2190</t>
+          <t>1047079d-3655-48f7-a34b-eddb993840fe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>76ac5cd1-8da8-4b52-a96f-cc3407f9656d</t>
+          <t>3da5b804-7070-40ce-b6a4-85ee0624c3f4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>414becf9-46b2-4d49-975d-ed962aa02e2e</t>
+          <t>9d38d112-d84f-4587-a1eb-5f180ef91214</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>f42a022f-4904-463a-a712-c4eee9a4adee</t>
+          <t>fddfcd28-4af5-4dd9-a9cd-d6387cae2d96</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4265653b-2ab6-4c65-9ac4-2e0d49e8af26</t>
+          <t>7224fc65-a6b6-4f78-a562-3d2d93565da1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>035f4bce-3ab1-47b3-bd32-823d20840663</t>
+          <t>966edd62-d24a-482b-b392-7b2fcc95e399</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4404b8f1-4e74-48b3-98b7-9f3c9dd05904</t>
+          <t>4b1121aa-27f1-4d4a-b8b4-b7bad0440b98</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>f7ba8901-0d96-4345-b7ab-60682f46043c</t>
+          <t>25acdad9-d2aa-4740-98de-f1b6fbd8dd44</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>76ac5cd1-8da8-4b52-a96f-cc3407f9656d</t>
+          <t>3da5b804-7070-40ce-b6a4-85ee0624c3f4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8fdc04be-69a2-46e9-8b9e-ff30499d50f9</t>
+          <t>5b347afa-fb7a-42e3-aa57-d2fe45b61bdf</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1064a4dc-df76-4aba-8b74-953a4c66fa16</t>
+          <t>29d3e3d9-da12-4f22-83f3-9671acea6310</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a4ec3ffd-ded5-46e4-a59b-aa115445671e</t>
+          <t>24a1abf4-b48c-4b9f-aba3-747874d27fc8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1582,7 +1582,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8fdc04be-69a2-46e9-8b9e-ff30499d50f9</t>
+          <t>5b347afa-fb7a-42e3-aa57-d2fe45b61bdf</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1594,7 +1594,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0225805e-e09b-468f-adad-065911af0217</t>
+          <t>df054142-130a-476c-a0ae-ac6df1aa5f8f</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>f847a690-1ac5-47d2-905e-9917fe9577ec</t>
+          <t>1915e96f-c0b7-491c-8f53-b9e523b3289e</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9d289793-678b-40a2-b426-6c3fd8ab7287</t>
+          <t>0a1c3544-80e9-4724-8dc7-bfb477c3bc7b</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>035f4bce-3ab1-47b3-bd32-823d20840663</t>
+          <t>966edd62-d24a-482b-b392-7b2fcc95e399</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0685e7f7-5ede-4cb7-9400-d6bbad7e5e85</t>
+          <t>5ebd7da5-db9a-4f69-b0e1-4f6f6fed6687</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5f5084ea-44de-4abb-a2bc-3e3d2cf71525</t>
+          <t>ff82fddb-b8ab-4f98-934a-a1a59d39b31b</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>008c0375-a8bb-43b1-bc1e-b501f053dd11</t>
+          <t>3a01efce-4062-4761-aca6-cb99a7c5b784</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>359a8f68-9347-468a-9e71-2fd7a932482a</t>
+          <t>9278f6ac-147a-4450-ad2f-0662a8bc8f3f</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8fdc04be-69a2-46e9-8b9e-ff30499d50f9</t>
+          <t>5b347afa-fb7a-42e3-aa57-d2fe45b61bdf</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01ec941f-3f3b-4f36-8fad-de4d338bd357</t>
+          <t>dc1118f3-cf2c-45a1-9e39-3401e91fac7b</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4f064491-1669-4b87-abc0-3677a36796f2</t>
+          <t>7436ad94-8385-4188-be19-cb60ce45a6b6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0c048e4b-9779-4b56-8089-73b90a95e7a9</t>
+          <t>24aec31b-be3f-4f45-9a82-08cf598a36c6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -1786,7 +1786,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>c1d763d6-6ebb-4d3e-9f69-dff7bfed3e5f</t>
+          <t>0e448ccb-621f-4403-8409-4fa5865b0393</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ce67cd45-33c4-4a42-a11c-0a7b1f525270</t>
+          <t>b4720f3e-9c23-4625-bbff-9fc4ea4d44f5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ec2ce638-c3ca-4bcd-bc4d-315fb7888955</t>
+          <t>6c950ef0-93d9-4237-bbf6-9f63b27c6658</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -1834,7 +1834,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>9aa3b6d8-bb97-45ce-9288-37bbeeb8a16c</t>
+          <t>b6302ed5-3c77-4247-a2b8-6f46e6e831b0</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9e1673c4-5a26-4f6f-9da5-afa55611f44f</t>
+          <t>cd30ce1b-d67a-45d3-9d1e-23219e0b9ed6</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>b6feb9d6-2504-46ca-bd63-cebf56ffa28e</t>
+          <t>01bd484f-97d8-4474-b008-4bb3e9277498</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>19ac85a0-482b-4e4e-9f9d-9373e5197444</t>
+          <t>d8f465df-92ad-4edf-b449-5592f265da83</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>008c0375-a8bb-43b1-bc1e-b501f053dd11</t>
+          <t>3a01efce-4062-4761-aca6-cb99a7c5b784</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>c2e04829-1cff-4b7c-be5b-849497be16c7</t>
+          <t>4b22a334-6bfd-4c50-9aec-6bebcc0f289a</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>93bdf5de-f329-4dce-8a5d-f66f4c0f146e</t>
+          <t>ea1e3465-fa8d-40fd-8444-1d53349b63a0</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4f71c126-6d02-4ff7-aa31-4a19ed2ac5dd</t>
+          <t>a894b03f-e16f-4784-84e8-6f01b9fb7c64</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -1954,7 +1954,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>d27be5c4-3d74-4264-a869-f5ca39930b8d</t>
+          <t>0065711e-d1b5-46aa-b654-f4ae232d118a</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5f5084ea-44de-4abb-a2bc-3e3d2cf71525</t>
+          <t>ff82fddb-b8ab-4f98-934a-a1a59d39b31b</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>d36fc989-0ebe-4ed1-b7ff-3a89ed08191a</t>
+          <t>d5bf0026-742b-4ea1-9fe3-8bdec31b0e45</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>a0c5442a-590b-4492-b39b-b9f0b2dda7e6</t>
+          <t>501223c5-277c-4a50-9279-4824abf36d22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>54fca07c-27a4-4f19-9e12-68cdab4aa082</t>
+          <t>e02d1641-7b75-4057-a560-ee615b79013f</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>53c8a748-12ff-41d6-a77c-e19254a0e736</t>
+          <t>911ec9c8-5ee5-4737-993d-a3f7550ba438</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>f7ba8901-0d96-4345-b7ab-60682f46043c</t>
+          <t>25acdad9-d2aa-4740-98de-f1b6fbd8dd44</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2050,7 +2050,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>b7728e62-2701-416d-8225-a4948fe51e3d</t>
+          <t>a2dff279-6159-48fb-9f29-f4b0b3f6ee8e</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>93bdf5de-f329-4dce-8a5d-f66f4c0f146e</t>
+          <t>ea1e3465-fa8d-40fd-8444-1d53349b63a0</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4af34c15-d5c9-462e-85e5-3f15cc0a9d0a</t>
+          <t>37b9167b-d0a7-4565-b505-737fee966821</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2086,7 +2086,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>f847a690-1ac5-47d2-905e-9917fe9577ec</t>
+          <t>1915e96f-c0b7-491c-8f53-b9e523b3289e</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>54223c7d-d72d-4573-8ad0-cac5f1b5e26a</t>
+          <t>311e1299-bc3b-4998-8f48-50e891cdc07e</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2158,7 +2158,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ccb23593-3e4d-4689-aa63-a27741a90d74</t>
+          <t>aa050ea9-0d9e-4a7f-8b39-78ee272ade87</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2182,7 +2182,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>b94d7678-c7b3-4089-bf10-cce1ac2cf847</t>
+          <t>179fd5e8-17f7-4bda-b761-f88b34275930</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>c3962538-4122-4793-95d5-a25b2bbfddd3</t>
+          <t>0720a591-d764-45d5-b013-490ebe382329</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>e6bd16d3-72d9-4190-adc3-e02385e02559</t>
+          <t>7b465454-1f04-449b-9af1-62d643ed8d41</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>b9b773f5-83ce-46c4-9100-cadfd3feb6b9</t>
+          <t>9d707078-25a1-47d8-973f-548785e302ca</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>79318d7c-34a2-4402-a8fd-72972d4f2034</t>
+          <t>c4d574bc-4850-480b-a55a-76aea655b9d6</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2242,7 +2242,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8ebc7d87-92ad-4ead-933b-756e3a609d5a</t>
+          <t>17cd22b6-3a11-4dfd-9395-242ce37db1c2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2266,7 +2266,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2278,7 +2278,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5687c94d-9565-4dfb-9767-b96009dcff3b</t>
+          <t>a1579a13-58ec-416d-b32f-e70df61c8c80</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>578ffa9d-ec4c-4a54-8a32-6f15ac4deb53</t>
+          <t>533d0a29-8ed3-4625-af16-a0f4f9e0c2f0</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>0225805e-e09b-468f-adad-065911af0217</t>
+          <t>df054142-130a-476c-a0ae-ac6df1aa5f8f</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2314,7 +2314,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>a52ab805-8822-4e48-a23a-58eb8d10a72f</t>
+          <t>4c2be30f-a0d3-4071-8d9c-c0c3b2f9a476</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>d27be5c4-3d74-4264-a869-f5ca39930b8d</t>
+          <t>0065711e-d1b5-46aa-b654-f4ae232d118a</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ef3426a4-3ea3-437f-b268-7f9f61ad0b89</t>
+          <t>78de78d2-45b5-4dfd-bd24-1ec1ad805b7b</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2362,7 +2362,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>256e4379-4f35-4087-9f22-73a7f915b208</t>
+          <t>c502c156-68f1-4ec6-9d48-c5454d99a25f</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>e5829554-d774-47f1-9e79-d3f0a703c22e</t>
+          <t>25b18c56-04e3-40a2-96c6-9f8b3a3bf3c4</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1e61c945-1942-4e78-b762-12a14b5dd95c</t>
+          <t>ec13fb11-8965-400b-b834-e3cbaa12604a</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -2422,7 +2422,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>0b8609f4-825b-4888-8e37-e56fdfefa560</t>
+          <t>d3fd41d5-7be6-42a4-9e28-e9b2b915dcc6</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -2434,7 +2434,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>32406004-545d-4484-b72d-b9914878670f</t>
+          <t>4fdbc0a2-8d61-4e97-927b-282b5df0b681</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -2446,7 +2446,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>105696b8-7c38-4fe5-92f5-3c6fb1268f48</t>
+          <t>e7867498-1e26-4f63-8ead-766e787f4bc7</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>50bd3176-47f2-4847-9260-492ed10c84f8</t>
+          <t>9027c945-7341-4149-be48-fd29fa26970d</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -2482,7 +2482,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2f983d15-b4b9-4a43-9ba2-f8d2334b2190</t>
+          <t>1047079d-3655-48f7-a34b-eddb993840fe</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>359a8f68-9347-468a-9e71-2fd7a932482a</t>
+          <t>9278f6ac-147a-4450-ad2f-0662a8bc8f3f</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -2506,7 +2506,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>dcb5ea48-dfc2-403d-8474-7ad1a810718f</t>
+          <t>d4939a6f-266a-4d53-af25-f7da292eb096</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>80fb4c6d-d5f8-42ed-b3c7-8a10596dd382</t>
+          <t>31fae897-0630-4862-aabf-e709ff39752b</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -2530,7 +2530,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5b0e86f3-4bdb-4998-b076-b9294b20086d</t>
+          <t>a68cd6ef-c68a-441e-a830-6b7cab96460a</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8d40dcb1-c873-4389-b9c7-5f0e14ee5cc3</t>
+          <t>f66e4871-3011-46d5-9eeb-9735ff2cc8a0</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>933ad94c-2e9f-485c-830a-2ca6c4230d39</t>
+          <t>7ff1ea7e-5828-4e1a-8090-df457f48018f</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1e61c945-1942-4e78-b762-12a14b5dd95c</t>
+          <t>ec13fb11-8965-400b-b834-e3cbaa12604a</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1d738d42-7ad4-4f7a-81b3-40d173b9bf4c</t>
+          <t>5fa2b00f-c96d-4135-ad06-df1c260cb724</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -2590,7 +2590,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ac743291-95ce-473e-b366-1688ea732dc5</t>
+          <t>e650fa23-f819-4333-8027-74c1e0030271</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>0c048e4b-9779-4b56-8089-73b90a95e7a9</t>
+          <t>24aec31b-be3f-4f45-9a82-08cf598a36c6</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1064a4dc-df76-4aba-8b74-953a4c66fa16</t>
+          <t>29d3e3d9-da12-4f22-83f3-9671acea6310</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -2638,7 +2638,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4265653b-2ab6-4c65-9ac4-2e0d49e8af26</t>
+          <t>7224fc65-a6b6-4f78-a562-3d2d93565da1</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -2650,7 +2650,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -2662,7 +2662,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>312876be-484d-47e9-8b5e-4522fad5df43</t>
+          <t>9614b009-6732-4501-bb01-9c3e282d45de</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>50bd3176-47f2-4847-9260-492ed10c84f8</t>
+          <t>9027c945-7341-4149-be48-fd29fa26970d</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6f98d296-c5e7-49d5-b34e-3a3f7c1e112b</t>
+          <t>006e14c2-2615-4cd8-bc46-77c4c58ead5a</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>32406004-545d-4484-b72d-b9914878670f</t>
+          <t>4fdbc0a2-8d61-4e97-927b-282b5df0b681</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>155e9331-3434-415f-9d66-67736534d80b</t>
+          <t>c79ca409-badc-4ec1-988b-e315cf9674cd</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>cea15e94-869f-417a-9ad4-a70aefc74f34</t>
+          <t>68ac6965-f822-4e2a-8394-c81b5bce9ac9</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>008c0375-a8bb-43b1-bc1e-b501f053dd11</t>
+          <t>3a01efce-4062-4761-aca6-cb99a7c5b784</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4404b8f1-4e74-48b3-98b7-9f3c9dd05904</t>
+          <t>4b1121aa-27f1-4d4a-b8b4-b7bad0440b98</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -2770,7 +2770,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>114e30a1-25ee-419c-814f-5fc37d86252a</t>
+          <t>f626081b-f710-4003-91b0-5471de681880</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8ab023f2-02a0-4d43-a38f-ea4087d71590</t>
+          <t>0e22e25a-5aee-480f-aebc-cc990d2c8aa6</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -2806,7 +2806,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>deae9658-89b8-4d8f-b35e-5d367e700074</t>
+          <t>9a5d69ae-2bb9-4bdf-ad9b-1eb5a3759959</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>50bd3176-47f2-4847-9260-492ed10c84f8</t>
+          <t>9027c945-7341-4149-be48-fd29fa26970d</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>e5829554-d774-47f1-9e79-d3f0a703c22e</t>
+          <t>25b18c56-04e3-40a2-96c6-9f8b3a3bf3c4</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -2842,7 +2842,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>32406004-545d-4484-b72d-b9914878670f</t>
+          <t>4fdbc0a2-8d61-4e97-927b-282b5df0b681</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5cbc5582-a71e-4818-b1f6-0786c89dbaf5</t>
+          <t>334bd034-b135-48e1-8d50-97ea54ec0493</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>0a7ccfb9-51a2-425b-97d0-defde3a02ce7</t>
+          <t>a1892263-2a24-43a1-8278-4c9cbf455d27</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -2878,7 +2878,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -2890,7 +2890,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>008c0375-a8bb-43b1-bc1e-b501f053dd11</t>
+          <t>3a01efce-4062-4761-aca6-cb99a7c5b784</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>d5139ff1-167a-492d-8eb0-ad2260ba4e6a</t>
+          <t>80d115ce-108c-4afe-bae4-421939aee10c</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>516be647-5631-4273-b5b1-436ad6372f65</t>
+          <t>992402c2-3081-49d5-883c-1df9e7a4f8ad</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -2938,7 +2938,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5e990adf-ce1e-4762-b61f-7615354e1877</t>
+          <t>c7e943af-05ea-41dd-aac7-792b383d64ba</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>c1d763d6-6ebb-4d3e-9f69-dff7bfed3e5f</t>
+          <t>0e448ccb-621f-4403-8409-4fa5865b0393</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3010,7 +3010,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2b190f8a-b46f-478d-a77d-199659aace3e</t>
+          <t>b940ec08-c742-493a-94e7-7d09ff0f275a</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3022,7 +3022,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>0225805e-e09b-468f-adad-065911af0217</t>
+          <t>df054142-130a-476c-a0ae-ac6df1aa5f8f</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8fdc04be-69a2-46e9-8b9e-ff30499d50f9</t>
+          <t>5b347afa-fb7a-42e3-aa57-d2fe45b61bdf</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8d809a57-cf18-4407-9304-70322ce327ea</t>
+          <t>1c3e188b-354a-47ff-b161-7e48b96cd2b7</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3058,7 +3058,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>0a3287b3-e72a-453b-9fa4-0f265bdaf2f4</t>
+          <t>fc4ceeb8-6af6-4380-8a4c-de8c167b00ab</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3070,7 +3070,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>a5e2cb8c-f9a7-4e47-afb8-c9e80e7fe925</t>
+          <t>a8930c88-2102-4ee8-897f-060e9f2d09b4</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3d97d1be-1614-4377-9296-631123088ed7</t>
+          <t>07dff28f-8f2c-448e-bbd8-d0234def6546</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3118,7 +3118,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>0c0b2c60-3611-4f01-ac5e-13f96ec38a03</t>
+          <t>37fa2ee6-3353-48eb-aebb-2ca06602bc59</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>31332c41-5a39-4bbc-b4be-f72dbe4cad91</t>
+          <t>afdd7ce9-0731-44e3-9885-66dac64bc25f</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4f71c126-6d02-4ff7-aa31-4a19ed2ac5dd</t>
+          <t>a894b03f-e16f-4784-84e8-6f01b9fb7c64</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>7978e4db-aa02-481f-a00e-7a31b33a8d57</t>
+          <t>76c21f8c-5942-4431-8178-b97a409b1c39</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3178,7 +3178,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>332359d5-e197-46aa-9a71-9268cc163430</t>
+          <t>950ea867-22bc-41a9-aa54-ed496cada75a</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>eb16c569-d25c-4bc1-bd2d-e124c7fffc31</t>
+          <t>2eaa7d6d-ba2b-47d5-9e17-423646a4fa8a</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>9721f3a7-07aa-4c78-8332-8d1ebfbf9d3a</t>
+          <t>eb4b3541-a786-4a3f-adf2-8ff4d17d6c27</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3214,7 +3214,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>485d6fb5-896c-41af-a87c-9efdd3edf92a</t>
+          <t>1e75f7bf-c89f-4366-b367-e68d7b757c47</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>d5139ff1-167a-492d-8eb0-ad2260ba4e6a</t>
+          <t>80d115ce-108c-4afe-bae4-421939aee10c</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>155e9331-3434-415f-9d66-67736534d80b</t>
+          <t>c79ca409-badc-4ec1-988b-e315cf9674cd</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>a1d1ef75-9769-4f60-9386-7b77c71a6639</t>
+          <t>5451b6e8-2a6b-4aef-9f6f-1c3e1e326643</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>035f4bce-3ab1-47b3-bd32-823d20840663</t>
+          <t>966edd62-d24a-482b-b392-7b2fcc95e399</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -3274,7 +3274,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>cd64afd4-6d2e-47ae-914f-e362d36ff1c0</t>
+          <t>3719e51d-2ddb-4cc9-b0dc-8a631a6d6291</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>eb16c569-d25c-4bc1-bd2d-e124c7fffc31</t>
+          <t>2eaa7d6d-ba2b-47d5-9e17-423646a4fa8a</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>c2e04829-1cff-4b7c-be5b-849497be16c7</t>
+          <t>4b22a334-6bfd-4c50-9aec-6bebcc0f289a</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -3346,7 +3346,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ec2ce638-c3ca-4bcd-bc4d-315fb7888955</t>
+          <t>6c950ef0-93d9-4237-bbf6-9f63b27c6658</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>256e4379-4f35-4087-9f22-73a7f915b208</t>
+          <t>c502c156-68f1-4ec6-9d48-c5454d99a25f</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>332359d5-e197-46aa-9a71-9268cc163430</t>
+          <t>950ea867-22bc-41a9-aa54-ed496cada75a</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -3406,7 +3406,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>0225805e-e09b-468f-adad-065911af0217</t>
+          <t>df054142-130a-476c-a0ae-ac6df1aa5f8f</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2d04733d-84ce-4f7d-968a-1a20a8662ef8</t>
+          <t>ec0861c9-656d-4302-a69a-cc085bb7b2a2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -3430,7 +3430,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>b7728e62-2701-416d-8225-a4948fe51e3d</t>
+          <t>a2dff279-6159-48fb-9f29-f4b0b3f6ee8e</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>a52ab805-8822-4e48-a23a-58eb8d10a72f</t>
+          <t>4c2be30f-a0d3-4071-8d9c-c0c3b2f9a476</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -3454,7 +3454,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4c97e299-4fba-4184-bb8d-f81a5ec031c8</t>
+          <t>e0b9741a-368d-4e3f-aadc-3a70d1e9c924</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>578ffa9d-ec4c-4a54-8a32-6f15ac4deb53</t>
+          <t>533d0a29-8ed3-4625-af16-a0f4f9e0c2f0</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>e5829554-d774-47f1-9e79-d3f0a703c22e</t>
+          <t>25b18c56-04e3-40a2-96c6-9f8b3a3bf3c4</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>19ac85a0-482b-4e4e-9f9d-9373e5197444</t>
+          <t>d8f465df-92ad-4edf-b449-5592f265da83</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -3514,7 +3514,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>029e663d-1331-4b50-8b19-2917d426d54d</t>
+          <t>d83e3592-11cf-4922-9167-dcabab8406da</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -3538,7 +3538,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>b6833cf4-b8d0-4afe-b282-558e7fa9fc4a</t>
+          <t>15264ee6-4d1e-4be0-91c3-c24447f181a7</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>d36fc989-0ebe-4ed1-b7ff-3a89ed08191a</t>
+          <t>d5bf0026-742b-4ea1-9fe3-8bdec31b0e45</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -3586,7 +3586,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>32406004-545d-4484-b72d-b9914878670f</t>
+          <t>4fdbc0a2-8d61-4e97-927b-282b5df0b681</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -3598,7 +3598,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -3610,7 +3610,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>12ad2f77-7cc9-47df-b4df-9f7f4a65c456</t>
+          <t>1f7ad398-0ce0-4edf-be08-00b4e5fe31d0</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>0225805e-e09b-468f-adad-065911af0217</t>
+          <t>df054142-130a-476c-a0ae-ac6df1aa5f8f</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>0a7ccfb9-51a2-425b-97d0-defde3a02ce7</t>
+          <t>a1892263-2a24-43a1-8278-4c9cbf455d27</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>f847a690-1ac5-47d2-905e-9917fe9577ec</t>
+          <t>1915e96f-c0b7-491c-8f53-b9e523b3289e</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -3658,7 +3658,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>76ac5cd1-8da8-4b52-a96f-cc3407f9656d</t>
+          <t>3da5b804-7070-40ce-b6a4-85ee0624c3f4</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>247fb26b-f717-43ec-b69e-5c4f51de13f6</t>
+          <t>1c4faf3d-b368-4544-9e4e-ec20c12bc05d</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -3682,7 +3682,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>78ac90d6-dd6d-4df9-97ad-ccdffe598e56</t>
+          <t>ce336072-f887-4479-b7e6-746a094e0c18</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -3706,7 +3706,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3d97d1be-1614-4377-9296-631123088ed7</t>
+          <t>07dff28f-8f2c-448e-bbd8-d0234def6546</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -3730,7 +3730,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>30c6b23a-f1fd-44bb-9515-47f6a8cb0957</t>
+          <t>225953ac-9d87-48ed-a3ec-01d24e60ec32</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2a09b322-5a26-4b2d-931f-00acf6f240ca</t>
+          <t>d5bd5578-d464-4892-ba21-ff6520d00d41</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -3754,7 +3754,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>fe7313b0-1e38-4c9a-a041-1d05e3476cb0</t>
+          <t>3715a8fb-5848-4cd7-8bcb-e84346465b69</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>029e663d-1331-4b50-8b19-2917d426d54d</t>
+          <t>d83e3592-11cf-4922-9167-dcabab8406da</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5cbc5582-a71e-4818-b1f6-0786c89dbaf5</t>
+          <t>334bd034-b135-48e1-8d50-97ea54ec0493</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -3790,7 +3790,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>312876be-484d-47e9-8b5e-4522fad5df43</t>
+          <t>9614b009-6732-4501-bb01-9c3e282d45de</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>256e4379-4f35-4087-9f22-73a7f915b208</t>
+          <t>c502c156-68f1-4ec6-9d48-c5454d99a25f</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8b0a0720-0487-44d2-9aae-32dfec5c4b5c</t>
+          <t>4be511d9-1baa-4ed1-8ce8-db7161fce0fe</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>79318d7c-34a2-4402-a8fd-72972d4f2034</t>
+          <t>c4d574bc-4850-480b-a55a-76aea655b9d6</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>cd64afd4-6d2e-47ae-914f-e362d36ff1c0</t>
+          <t>3719e51d-2ddb-4cc9-b0dc-8a631a6d6291</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>4265653b-2ab6-4c65-9ac4-2e0d49e8af26</t>
+          <t>7224fc65-a6b6-4f78-a562-3d2d93565da1</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -3874,7 +3874,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>d36fc989-0ebe-4ed1-b7ff-3a89ed08191a</t>
+          <t>d5bf0026-742b-4ea1-9fe3-8bdec31b0e45</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -3886,7 +3886,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -3898,7 +3898,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>044184fb-4b4f-45c1-a7b9-714ff1f2decf</t>
+          <t>65cb4339-2e57-43a8-9997-b4051b483a5e</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -3922,7 +3922,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>247fb26b-f717-43ec-b69e-5c4f51de13f6</t>
+          <t>1c4faf3d-b368-4544-9e4e-ec20c12bc05d</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -3946,7 +3946,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2a09b322-5a26-4b2d-931f-00acf6f240ca</t>
+          <t>d5bd5578-d464-4892-ba21-ff6520d00d41</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5b0e86f3-4bdb-4998-b076-b9294b20086d</t>
+          <t>a68cd6ef-c68a-441e-a830-6b7cab96460a</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>c1d763d6-6ebb-4d3e-9f69-dff7bfed3e5f</t>
+          <t>0e448ccb-621f-4403-8409-4fa5865b0393</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -3994,7 +3994,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>eb16c569-d25c-4bc1-bd2d-e124c7fffc31</t>
+          <t>2eaa7d6d-ba2b-47d5-9e17-423646a4fa8a</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8ab023f2-02a0-4d43-a38f-ea4087d71590</t>
+          <t>0e22e25a-5aee-480f-aebc-cc990d2c8aa6</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -4018,7 +4018,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1609fdd7-29c6-4678-84af-30684d709f0b</t>
+          <t>d69b50f2-d432-4e62-8eb6-544c16ea8f91</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -4030,7 +4030,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4f71c126-6d02-4ff7-aa31-4a19ed2ac5dd</t>
+          <t>a894b03f-e16f-4784-84e8-6f01b9fb7c64</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>0c048e4b-9779-4b56-8089-73b90a95e7a9</t>
+          <t>24aec31b-be3f-4f45-9a82-08cf598a36c6</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -4066,7 +4066,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4c97e299-4fba-4184-bb8d-f81a5ec031c8</t>
+          <t>e0b9741a-368d-4e3f-aadc-3a70d1e9c924</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>a06d42ce-eecc-45d6-83d6-37c2acbe4778</t>
+          <t>33281820-0832-461e-aadd-9fbb4bf24b59</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -4090,7 +4090,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>d27be5c4-3d74-4264-a869-f5ca39930b8d</t>
+          <t>0065711e-d1b5-46aa-b654-f4ae232d118a</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>c2e04829-1cff-4b7c-be5b-849497be16c7</t>
+          <t>4b22a334-6bfd-4c50-9aec-6bebcc0f289a</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8b0a0720-0487-44d2-9aae-32dfec5c4b5c</t>
+          <t>4be511d9-1baa-4ed1-8ce8-db7161fce0fe</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>e5829554-d774-47f1-9e79-d3f0a703c22e</t>
+          <t>25b18c56-04e3-40a2-96c6-9f8b3a3bf3c4</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -4138,7 +4138,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2f983d15-b4b9-4a43-9ba2-f8d2334b2190</t>
+          <t>1047079d-3655-48f7-a34b-eddb993840fe</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -4150,7 +4150,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4f71c126-6d02-4ff7-aa31-4a19ed2ac5dd</t>
+          <t>a894b03f-e16f-4784-84e8-6f01b9fb7c64</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -4162,7 +4162,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>247fb26b-f717-43ec-b69e-5c4f51de13f6</t>
+          <t>1c4faf3d-b368-4544-9e4e-ec20c12bc05d</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>d27be5c4-3d74-4264-a869-f5ca39930b8d</t>
+          <t>0065711e-d1b5-46aa-b654-f4ae232d118a</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>76ac5cd1-8da8-4b52-a96f-cc3407f9656d</t>
+          <t>3da5b804-7070-40ce-b6a4-85ee0624c3f4</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>30c6b23a-f1fd-44bb-9515-47f6a8cb0957</t>
+          <t>225953ac-9d87-48ed-a3ec-01d24e60ec32</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -4222,7 +4222,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>0cf61d40-8086-498c-8cc9-ba7abcadd7f5</t>
+          <t>b65bb17a-7601-4b84-be0b-a119c4b1ec87</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -4234,7 +4234,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>deae9658-89b8-4d8f-b35e-5d367e700074</t>
+          <t>9a5d69ae-2bb9-4bdf-ad9b-1eb5a3759959</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>dd195d60-07c7-4d82-bc37-8489acc53c88</t>
+          <t>e1b40bc8-4f64-44be-aeb7-8717aa138385</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6f98d296-c5e7-49d5-b34e-3a3f7c1e112b</t>
+          <t>006e14c2-2615-4cd8-bc46-77c4c58ead5a</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -4270,7 +4270,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -4282,7 +4282,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>516be647-5631-4273-b5b1-436ad6372f65</t>
+          <t>992402c2-3081-49d5-883c-1df9e7a4f8ad</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -4294,7 +4294,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>30c6b23a-f1fd-44bb-9515-47f6a8cb0957</t>
+          <t>225953ac-9d87-48ed-a3ec-01d24e60ec32</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -4306,7 +4306,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>f847a690-1ac5-47d2-905e-9917fe9577ec</t>
+          <t>1915e96f-c0b7-491c-8f53-b9e523b3289e</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -4330,7 +4330,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>77051adf-48d3-46db-acce-a5b9706579fc</t>
+          <t>52c218b7-7515-4570-ac82-b012d0b9283c</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -4342,7 +4342,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -4354,7 +4354,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>19ac85a0-482b-4e4e-9f9d-9373e5197444</t>
+          <t>d8f465df-92ad-4edf-b449-5592f265da83</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>029e663d-1331-4b50-8b19-2917d426d54d</t>
+          <t>d83e3592-11cf-4922-9167-dcabab8406da</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>256e4379-4f35-4087-9f22-73a7f915b208</t>
+          <t>c502c156-68f1-4ec6-9d48-c5454d99a25f</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -4426,7 +4426,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>578ffa9d-ec4c-4a54-8a32-6f15ac4deb53</t>
+          <t>533d0a29-8ed3-4625-af16-a0f4f9e0c2f0</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>19ac85a0-482b-4e4e-9f9d-9373e5197444</t>
+          <t>d8f465df-92ad-4edf-b449-5592f265da83</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -4450,7 +4450,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>e7c4fa66-6c18-46f3-81b1-628cf18e6879</t>
+          <t>e51635bd-b79e-404a-aac9-9b79435be8fa</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -4474,7 +4474,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>30c6b23a-f1fd-44bb-9515-47f6a8cb0957</t>
+          <t>225953ac-9d87-48ed-a3ec-01d24e60ec32</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>9721f3a7-07aa-4c78-8332-8d1ebfbf9d3a</t>
+          <t>eb4b3541-a786-4a3f-adf2-8ff4d17d6c27</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -4498,7 +4498,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -4510,7 +4510,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2f983d15-b4b9-4a43-9ba2-f8d2334b2190</t>
+          <t>1047079d-3655-48f7-a34b-eddb993840fe</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>d5139ff1-167a-492d-8eb0-ad2260ba4e6a</t>
+          <t>80d115ce-108c-4afe-bae4-421939aee10c</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -4558,7 +4558,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>b3eb37b0-6525-4ef6-829a-0a98b06cf525</t>
+          <t>d3b64cd8-eea7-4fa6-8765-64a834e023ce</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -4570,7 +4570,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2a09b322-5a26-4b2d-931f-00acf6f240ca</t>
+          <t>d5bd5578-d464-4892-ba21-ff6520d00d41</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -4582,7 +4582,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>8270589d-2740-4602-be1f-15d687a1655f</t>
+          <t>5ac05890-9953-4243-abd3-387ccd4a62b0</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>dcb5ea48-dfc2-403d-8474-7ad1a810718f</t>
+          <t>d4939a6f-266a-4d53-af25-f7da292eb096</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>c2c35ce8-4bdf-4ea6-a543-8ea8ede8a85c</t>
+          <t>04e30d9c-988a-4dc2-87dd-fae04fd7fd1b</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -4630,7 +4630,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -4642,7 +4642,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>54fca07c-27a4-4f19-9e12-68cdab4aa082</t>
+          <t>e02d1641-7b75-4057-a560-ee615b79013f</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -4654,7 +4654,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>53c8a748-12ff-41d6-a77c-e19254a0e736</t>
+          <t>911ec9c8-5ee5-4737-993d-a3f7550ba438</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -4678,7 +4678,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>e6bd16d3-72d9-4190-adc3-e02385e02559</t>
+          <t>7b465454-1f04-449b-9af1-62d643ed8d41</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>b94d7678-c7b3-4089-bf10-cce1ac2cf847</t>
+          <t>179fd5e8-17f7-4bda-b761-f88b34275930</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>0b8609f4-825b-4888-8e37-e56fdfefa560</t>
+          <t>d3fd41d5-7be6-42a4-9e28-e9b2b915dcc6</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ec2ce638-c3ca-4bcd-bc4d-315fb7888955</t>
+          <t>6c950ef0-93d9-4237-bbf6-9f63b27c6658</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2d04733d-84ce-4f7d-968a-1a20a8662ef8</t>
+          <t>ec0861c9-656d-4302-a69a-cc085bb7b2a2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>64624d25-3946-4c8d-af3b-691980b8a95c</t>
+          <t>0028f537-a92a-4a9c-8e33-c864fead020f</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -4750,7 +4750,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>e6bd16d3-72d9-4190-adc3-e02385e02559</t>
+          <t>7b465454-1f04-449b-9af1-62d643ed8d41</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -4762,7 +4762,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -4774,7 +4774,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>dfc5a0a3-caee-489e-8ef5-72634d8ed054</t>
+          <t>5485acfb-2ee8-4d3f-9ddd-7a184ea4d0c1</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5d98b095-3f90-449f-884d-63c60cdeaa87</t>
+          <t>4bd96d87-3074-4a30-a963-6eb573a2397f</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>0cf61d40-8086-498c-8cc9-ba7abcadd7f5</t>
+          <t>b65bb17a-7601-4b84-be0b-a119c4b1ec87</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5bf6ba0f-90e1-4d9d-9561-88e4bfb683e9</t>
+          <t>ae2bd5fe-0008-46f7-8de3-31360de677da</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>f1f3bf6d-5749-4901-8a2d-4468aded6e38</t>
+          <t>0cb2211e-6c97-4720-97e4-583c2ea79457</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -4846,7 +4846,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>4404b8f1-4e74-48b3-98b7-9f3c9dd05904</t>
+          <t>4b1121aa-27f1-4d4a-b8b4-b7bad0440b98</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -4858,7 +4858,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>247fb26b-f717-43ec-b69e-5c4f51de13f6</t>
+          <t>1c4faf3d-b368-4544-9e4e-ec20c12bc05d</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>80fb4c6d-d5f8-42ed-b3c7-8a10596dd382</t>
+          <t>31fae897-0630-4862-aabf-e709ff39752b</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -4882,7 +4882,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -4894,7 +4894,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>3a7e16bf-a833-42ac-831b-e583c0800e61</t>
+          <t>07bccb94-0c12-4fa0-b866-048a07b43173</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -4918,7 +4918,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5aef1e86-5234-4dff-823e-d2c353f56905</t>
+          <t>de1a1e1d-d949-4b5c-b978-221ff5f831b7</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>dd195d60-07c7-4d82-bc37-8489acc53c88</t>
+          <t>e1b40bc8-4f64-44be-aeb7-8717aa138385</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>0b8609f4-825b-4888-8e37-e56fdfefa560</t>
+          <t>d3fd41d5-7be6-42a4-9e28-e9b2b915dcc6</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>32406004-545d-4484-b72d-b9914878670f</t>
+          <t>4fdbc0a2-8d61-4e97-927b-282b5df0b681</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>cceb8b80-957e-4609-9be3-926ea42b40c3</t>
+          <t>584a6a4b-cdef-4863-9d23-0ce190708847</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -5014,7 +5014,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3a7e16bf-a833-42ac-831b-e583c0800e61</t>
+          <t>07bccb94-0c12-4fa0-b866-048a07b43173</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -5026,7 +5026,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2b190f8a-b46f-478d-a77d-199659aace3e</t>
+          <t>b940ec08-c742-493a-94e7-7d09ff0f275a</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -5050,7 +5050,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>75ba12c8-4bcf-46d3-a232-8ceea4f98469</t>
+          <t>24fcc1cf-9d5a-4a7f-9152-10cb2cebe997</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -5062,7 +5062,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>64624d25-3946-4c8d-af3b-691980b8a95c</t>
+          <t>0028f537-a92a-4a9c-8e33-c864fead020f</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -5098,7 +5098,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>b6feb9d6-2504-46ca-bd63-cebf56ffa28e</t>
+          <t>01bd484f-97d8-4474-b008-4bb3e9277498</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -5110,7 +5110,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>312876be-484d-47e9-8b5e-4522fad5df43</t>
+          <t>9614b009-6732-4501-bb01-9c3e282d45de</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>b3eb37b0-6525-4ef6-829a-0a98b06cf525</t>
+          <t>d3b64cd8-eea7-4fa6-8765-64a834e023ce</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>029e663d-1331-4b50-8b19-2917d426d54d</t>
+          <t>d83e3592-11cf-4922-9167-dcabab8406da</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>53c8a748-12ff-41d6-a77c-e19254a0e736</t>
+          <t>911ec9c8-5ee5-4737-993d-a3f7550ba438</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -5158,7 +5158,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>59f1f608-c118-46f1-98e7-10220e74c56d</t>
+          <t>021f8369-2c39-42ce-8784-3eadc8b33980</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4404b8f1-4e74-48b3-98b7-9f3c9dd05904</t>
+          <t>4b1121aa-27f1-4d4a-b8b4-b7bad0440b98</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -5182,7 +5182,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>b94d7678-c7b3-4089-bf10-cce1ac2cf847</t>
+          <t>179fd5e8-17f7-4bda-b761-f88b34275930</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ed34a3a2-770e-464a-84cf-b42a452856b9</t>
+          <t>7e7e08e2-280e-416d-b965-00ad4463cad0</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1d738d42-7ad4-4f7a-81b3-40d173b9bf4c</t>
+          <t>5fa2b00f-c96d-4135-ad06-df1c260cb724</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -5218,7 +5218,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>d5139ff1-167a-492d-8eb0-ad2260ba4e6a</t>
+          <t>80d115ce-108c-4afe-bae4-421939aee10c</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -5230,7 +5230,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -5242,7 +5242,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>7978e4db-aa02-481f-a00e-7a31b33a8d57</t>
+          <t>76c21f8c-5942-4431-8178-b97a409b1c39</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>171a3faa-34f8-427a-9562-9cd4b87046d2</t>
+          <t>131b65e9-770c-46db-835f-d82e3f1072ac</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>8ebc7d87-92ad-4ead-933b-756e3a609d5a</t>
+          <t>17cd22b6-3a11-4dfd-9395-242ce37db1c2</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>54fca07c-27a4-4f19-9e12-68cdab4aa082</t>
+          <t>e02d1641-7b75-4057-a560-ee615b79013f</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -5290,7 +5290,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>8270589d-2740-4602-be1f-15d687a1655f</t>
+          <t>5ac05890-9953-4243-abd3-387ccd4a62b0</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>99968b43-9b08-4994-8bd8-19c05bb31aad</t>
+          <t>49ee59d3-b294-481b-b9ac-3efa022a9a93</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -5326,7 +5326,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>0c048e4b-9779-4b56-8089-73b90a95e7a9</t>
+          <t>24aec31b-be3f-4f45-9a82-08cf598a36c6</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -5362,7 +5362,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>40c6d9bd-cdd4-431a-b647-133e7bd7e7b2</t>
+          <t>29e3e122-d71c-47a8-aebb-7638a22db77c</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>171a3faa-34f8-427a-9562-9cd4b87046d2</t>
+          <t>131b65e9-770c-46db-835f-d82e3f1072ac</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -5386,7 +5386,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>f847a690-1ac5-47d2-905e-9917fe9577ec</t>
+          <t>1915e96f-c0b7-491c-8f53-b9e523b3289e</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -5398,7 +5398,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>59f1f608-c118-46f1-98e7-10220e74c56d</t>
+          <t>021f8369-2c39-42ce-8784-3eadc8b33980</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5dc9fb99-d6c3-4971-b7ec-aba506bbe817</t>
+          <t>0103ea27-9ced-490d-8b94-0d1f9b76e844</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>4c97e299-4fba-4184-bb8d-f81a5ec031c8</t>
+          <t>e0b9741a-368d-4e3f-aadc-3a70d1e9c924</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -5482,7 +5482,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>b764e16a-1eed-4aa2-ba44-3334531141a9</t>
+          <t>f88af1aa-b557-42d3-8b8a-9e1549fcb4af</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -5494,7 +5494,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -5506,7 +5506,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -5518,7 +5518,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>c2c35ce8-4bdf-4ea6-a543-8ea8ede8a85c</t>
+          <t>04e30d9c-988a-4dc2-87dd-fae04fd7fd1b</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>0a7ccfb9-51a2-425b-97d0-defde3a02ce7</t>
+          <t>a1892263-2a24-43a1-8278-4c9cbf455d27</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>a0c5442a-590b-4492-b39b-b9f0b2dda7e6</t>
+          <t>501223c5-277c-4a50-9279-4824abf36d22</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>7709b21e-401e-4fe3-9291-0515c6374195</t>
+          <t>3f10b256-d695-4aef-9528-3afda865799d</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -5578,7 +5578,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -5590,7 +5590,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>0685e7f7-5ede-4cb7-9400-d6bbad7e5e85</t>
+          <t>5ebd7da5-db9a-4f69-b0e1-4f6f6fed6687</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>cea15e94-869f-417a-9ad4-a70aefc74f34</t>
+          <t>68ac6965-f822-4e2a-8394-c81b5bce9ac9</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -5614,7 +5614,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>53c8a748-12ff-41d6-a77c-e19254a0e736</t>
+          <t>911ec9c8-5ee5-4737-993d-a3f7550ba438</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -5638,7 +5638,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1064a4dc-df76-4aba-8b74-953a4c66fa16</t>
+          <t>29d3e3d9-da12-4f22-83f3-9671acea6310</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -5650,7 +5650,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>044184fb-4b4f-45c1-a7b9-714ff1f2decf</t>
+          <t>65cb4339-2e57-43a8-9997-b4051b483a5e</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -5662,7 +5662,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>273ea3e0-399a-46af-a41e-52be0f3132f5</t>
+          <t>85c280f3-8c01-405d-9880-372bd01616fc</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -5698,7 +5698,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ed34a3a2-770e-464a-84cf-b42a452856b9</t>
+          <t>7e7e08e2-280e-416d-b965-00ad4463cad0</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -5722,7 +5722,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>029e663d-1331-4b50-8b19-2917d426d54d</t>
+          <t>d83e3592-11cf-4922-9167-dcabab8406da</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -5734,7 +5734,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>80fb4c6d-d5f8-42ed-b3c7-8a10596dd382</t>
+          <t>31fae897-0630-4862-aabf-e709ff39752b</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>12175814-556e-4e1a-af05-0c38c13e98a0</t>
+          <t>aacac9c8-54cd-4409-bdfe-f60c5e965799</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -5770,7 +5770,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>414becf9-46b2-4d49-975d-ed962aa02e2e</t>
+          <t>9d38d112-d84f-4587-a1eb-5f180ef91214</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -5782,7 +5782,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>7978e4db-aa02-481f-a00e-7a31b33a8d57</t>
+          <t>76c21f8c-5942-4431-8178-b97a409b1c39</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -5794,7 +5794,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>0685e7f7-5ede-4cb7-9400-d6bbad7e5e85</t>
+          <t>5ebd7da5-db9a-4f69-b0e1-4f6f6fed6687</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>fe7313b0-1e38-4c9a-a041-1d05e3476cb0</t>
+          <t>3715a8fb-5848-4cd7-8bcb-e84346465b69</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>103d2e66-b4a4-46c5-903b-f9fd4bf4ff96</t>
+          <t>51a6336d-c2cb-47ea-823c-643e3ddd091a</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2d04733d-84ce-4f7d-968a-1a20a8662ef8</t>
+          <t>ec0861c9-656d-4302-a69a-cc085bb7b2a2</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>4c97e299-4fba-4184-bb8d-f81a5ec031c8</t>
+          <t>e0b9741a-368d-4e3f-aadc-3a70d1e9c924</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -5854,7 +5854,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>8ab023f2-02a0-4d43-a38f-ea4087d71590</t>
+          <t>0e22e25a-5aee-480f-aebc-cc990d2c8aa6</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -5866,7 +5866,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>e5829554-d774-47f1-9e79-d3f0a703c22e</t>
+          <t>25b18c56-04e3-40a2-96c6-9f8b3a3bf3c4</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -5878,7 +5878,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2d04733d-84ce-4f7d-968a-1a20a8662ef8</t>
+          <t>ec0861c9-656d-4302-a69a-cc085bb7b2a2</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -5902,7 +5902,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ba5b0aaf-6570-47b5-aae2-33a4879a4f67</t>
+          <t>8472c407-79ed-4728-b405-c1fc18af15ef</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -5914,7 +5914,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>30c6b23a-f1fd-44bb-9515-47f6a8cb0957</t>
+          <t>225953ac-9d87-48ed-a3ec-01d24e60ec32</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>743ebbe2-c569-42ff-9b38-97d00679e408</t>
+          <t>e7831ae5-cf51-447e-a958-094bdc1e5a3e</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -5938,7 +5938,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>f7c6bd93-12b3-423b-bb1a-64378f265460</t>
+          <t>33547c5b-d803-4f16-b0c2-40a2267f86d4</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>ffa7d52b-efc8-4689-b7e2-d12877bfeb6a</t>
+          <t>5b5ab4de-dd5f-4153-96d2-3a6e0cd7eae1</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -5962,7 +5962,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>359a8f68-9347-468a-9e71-2fd7a932482a</t>
+          <t>9278f6ac-147a-4450-ad2f-0662a8bc8f3f</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -5974,7 +5974,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>53c8a748-12ff-41d6-a77c-e19254a0e736</t>
+          <t>911ec9c8-5ee5-4737-993d-a3f7550ba438</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>256e4379-4f35-4087-9f22-73a7f915b208</t>
+          <t>c502c156-68f1-4ec6-9d48-c5454d99a25f</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -5998,7 +5998,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>753346d7-9c10-4210-ba12-85d8f2ec1828</t>
+          <t>a241f601-d9dd-4376-b037-a57cecb141c6</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2cb631e2-7016-4b8e-b759-ea58d891b149</t>
+          <t>4ff6fc41-7df2-4877-9fe8-ae463642bc97</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -6022,7 +6022,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>d1d030be-d817-4d40-8e3b-0fb1bb34e56b</t>
+          <t>5e376c24-951e-4ed3-b2bf-23727c29de3a</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -6034,7 +6034,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>a52ab805-8822-4e48-a23a-58eb8d10a72f</t>
+          <t>4c2be30f-a0d3-4071-8d9c-c0c3b2f9a476</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>414becf9-46b2-4d49-975d-ed962aa02e2e</t>
+          <t>9d38d112-d84f-4587-a1eb-5f180ef91214</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -6058,7 +6058,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ed34a3a2-770e-464a-84cf-b42a452856b9</t>
+          <t>7e7e08e2-280e-416d-b965-00ad4463cad0</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -6070,7 +6070,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>348651a5-8a5a-4311-b999-4dfba846a413</t>
+          <t>da6c55c5-8922-4269-88df-90b56bfa5d3d</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>c80933ba-83f7-40d6-81c3-6f9835e77591</t>
+          <t>da043835-4ad6-4c2c-bd9c-28cac971e125</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -6094,7 +6094,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>dd195d60-07c7-4d82-bc37-8489acc53c88</t>
+          <t>e1b40bc8-4f64-44be-aeb7-8717aa138385</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -6106,7 +6106,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>cd64afd4-6d2e-47ae-914f-e362d36ff1c0</t>
+          <t>3719e51d-2ddb-4cc9-b0dc-8a631a6d6291</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -6118,7 +6118,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>9a072dbe-584f-43c4-978b-88dd092f9c90</t>
+          <t>11f2d634-c9ef-4583-ad95-25ca251bd062</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -6130,7 +6130,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>eca54c99-a0fb-4450-9c17-076d0cc34b98</t>
+          <t>3f0fd1da-ebc4-40e2-9ba2-34fdce9e719d</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>ed34a3a2-770e-464a-84cf-b42a452856b9</t>
+          <t>7e7e08e2-280e-416d-b965-00ad4463cad0</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -6154,7 +6154,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>933ad94c-2e9f-485c-830a-2ca6c4230d39</t>
+          <t>7ff1ea7e-5828-4e1a-8090-df457f48018f</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>187af54f-3ae0-4da0-a539-380cbbc3e879</t>
+          <t>74d1c86f-5d07-4179-a5e7-89ee29ac61a7</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>4404b8f1-4e74-48b3-98b7-9f3c9dd05904</t>
+          <t>4b1121aa-27f1-4d4a-b8b4-b7bad0440b98</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -6190,7 +6190,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>80c4bd83-407a-4f33-a0cc-7f1ac833143e</t>
+          <t>81c39583-d133-44d6-9776-586a9388c5ad</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -6214,7 +6214,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>0cf61d40-8086-498c-8cc9-ba7abcadd7f5</t>
+          <t>b65bb17a-7601-4b84-be0b-a119c4b1ec87</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -6226,7 +6226,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>359a8f68-9347-468a-9e71-2fd7a932482a</t>
+          <t>9278f6ac-147a-4450-ad2f-0662a8bc8f3f</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -6238,7 +6238,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>c1d763d6-6ebb-4d3e-9f69-dff7bfed3e5f</t>
+          <t>0e448ccb-621f-4403-8409-4fa5865b0393</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>82d8b3ad-a725-4f7e-b00c-3128caba5248</t>
+          <t>c85c477f-5ac5-4f69-875b-5dfb1db15d60</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -6262,7 +6262,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1b9e7ffb-accf-40e5-b257-bdd8b43f13eb</t>
+          <t>50b00ba3-c048-4c3c-978c-554071a7111b</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -6274,7 +6274,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>19ac85a0-482b-4e4e-9f9d-9373e5197444</t>
+          <t>d8f465df-92ad-4edf-b449-5592f265da83</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6aeebb03-c4b6-4c15-a2ef-b54608e791d1</t>
+          <t>993f40a8-a5c1-42c4-be92-2fd14e847543</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>155e9331-3434-415f-9d66-67736534d80b</t>
+          <t>c79ca409-badc-4ec1-988b-e315cf9674cd</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>59f1f608-c118-46f1-98e7-10220e74c56d</t>
+          <t>021f8369-2c39-42ce-8784-3eadc8b33980</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>01ec941f-3f3b-4f36-8fad-de4d338bd357</t>
+          <t>dc1118f3-cf2c-45a1-9e39-3401e91fac7b</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -6334,7 +6334,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>5b0e86f3-4bdb-4998-b076-b9294b20086d</t>
+          <t>a68cd6ef-c68a-441e-a830-6b7cab96460a</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>9d289793-678b-40a2-b426-6c3fd8ab7287</t>
+          <t>0a1c3544-80e9-4724-8dc7-bfb477c3bc7b</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -6358,7 +6358,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5a59e89d-74a8-4ab0-9c38-4b152438faf8</t>
+          <t>153293f0-d3cd-478f-8c3e-8c117d3ed7a8</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
